--- a/Hardware/BMU BOM.xlsx
+++ b/Hardware/BMU BOM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\15293\Desktop\ECE412-3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB872410-C5B8-4DC7-9B8B-98BD40C0345A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9F73E18-C2A4-4965-BBA5-22F54BA03FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="161">
   <si>
     <t>Item</t>
   </si>
@@ -505,6 +505,9 @@
   </si>
   <si>
     <t>BMU BOM</t>
+  </si>
+  <si>
+    <t>Link</t>
   </si>
 </sst>
 </file>
@@ -575,7 +578,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -869,7 +872,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.06640625" style="1"/>
@@ -883,7 +886,7 @@
     <col min="9" max="9" width="29.53125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" ht="25.5">
+    <row r="1" spans="1:10" s="2" customFormat="1" ht="25.5">
       <c r="A1" s="6" t="s">
         <v>159</v>
       </c>
@@ -895,8 +898,9 @@
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="6"/>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -924,8 +928,11 @@
       <c r="I2" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="J2" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -954,7 +961,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:10">
       <c r="A4" s="4">
         <v>2</v>
       </c>
@@ -983,7 +990,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:10">
       <c r="A5" s="4">
         <v>3</v>
       </c>
@@ -1012,7 +1019,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:10">
       <c r="A6" s="4">
         <v>4</v>
       </c>
@@ -1041,7 +1048,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:10">
       <c r="A7" s="4">
         <v>5</v>
       </c>
@@ -1070,7 +1077,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:10">
       <c r="A8" s="4">
         <v>6</v>
       </c>
@@ -1099,7 +1106,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:10">
       <c r="A9" s="4">
         <v>7</v>
       </c>
@@ -1128,7 +1135,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:10">
       <c r="A10" s="4">
         <v>8</v>
       </c>
@@ -1157,7 +1164,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:10">
       <c r="A11" s="4">
         <v>9</v>
       </c>
@@ -1186,7 +1193,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:10">
       <c r="A12" s="4">
         <v>10</v>
       </c>
@@ -1215,7 +1222,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:10">
       <c r="A13" s="4">
         <v>11</v>
       </c>
@@ -1244,7 +1251,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:10">
       <c r="A14" s="4">
         <v>12</v>
       </c>
@@ -1273,7 +1280,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:10">
       <c r="A15" s="4">
         <v>13</v>
       </c>
@@ -1302,7 +1309,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:10">
       <c r="A16" s="4">
         <v>14</v>
       </c>
@@ -1971,7 +1978,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
